--- a/equipe/Eudes_Juvencio.xlsx
+++ b/equipe/Eudes_Juvencio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexandre.celedonio\Desktop\meu_primeiro_dash\equipe\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SuporteLead\Desktop\dashboard_analytics\equipe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A26A230-3A3F-461D-BAED-E12E01EC596D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD42B7A6-3114-4FD5-9FE4-436AF4CA9A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{28FD2BDB-A87A-4B85-B83E-1AF1E0432417}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{28FD2BDB-A87A-4B85-B83E-1AF1E0432417}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
   <si>
     <t xml:space="preserve">Quarter </t>
   </si>
@@ -668,9 +668,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3BBC0EC-4B68-4267-A4DE-93B060F11E7E}">
   <dimension ref="A1:R13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -723,7 +723,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>16</v>
       </c>
@@ -775,7 +775,7 @@
         <v>636954</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>16</v>
       </c>
@@ -827,32 +827,58 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="11"/>
+      <c r="C4" s="5">
+        <v>35</v>
+      </c>
+      <c r="D4" s="5">
+        <v>37</v>
+      </c>
+      <c r="E4" s="6">
+        <v>7</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="6">
+        <v>3</v>
+      </c>
+      <c r="H4" s="6">
+        <v>7</v>
+      </c>
+      <c r="I4" s="8">
+        <v>2.33</v>
+      </c>
+      <c r="J4" s="9">
+        <v>0</v>
+      </c>
+      <c r="K4" s="9">
+        <v>0</v>
+      </c>
+      <c r="L4" s="9">
+        <v>0</v>
+      </c>
+      <c r="M4" s="9">
+        <v>0</v>
+      </c>
+      <c r="N4" s="10">
+        <v>0</v>
+      </c>
+      <c r="O4" s="11">
+        <v>0</v>
+      </c>
       <c r="P4" s="5"/>
       <c r="R4" s="17" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
@@ -874,7 +900,7 @@
       <c r="O5" s="11"/>
       <c r="P5" s="5"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="13" t="s">
         <v>22</v>
       </c>
@@ -896,7 +922,7 @@
       <c r="O6" s="11"/>
       <c r="P6" s="5"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" s="13" t="s">
         <v>22</v>
       </c>
@@ -918,7 +944,7 @@
       <c r="O7" s="11"/>
       <c r="P7" s="5"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8" s="13" t="s">
         <v>22</v>
       </c>
@@ -940,7 +966,7 @@
       <c r="O8" s="11"/>
       <c r="P8" s="5"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
         <v>26</v>
       </c>
@@ -962,7 +988,7 @@
       <c r="O9" s="11"/>
       <c r="P9" s="5"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A10" s="14" t="s">
         <v>26</v>
       </c>
@@ -984,7 +1010,7 @@
       <c r="O10" s="11"/>
       <c r="P10" s="5"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A11" s="14" t="s">
         <v>26</v>
       </c>
@@ -1006,7 +1032,7 @@
       <c r="O11" s="11"/>
       <c r="P11" s="5"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
         <v>30</v>
       </c>
@@ -1028,7 +1054,7 @@
       <c r="O12" s="11"/>
       <c r="P12" s="5"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
         <v>30</v>
       </c>
